--- a/14_stocks_analysis/01_rankings_sector/2604_.xlsx
+++ b/14_stocks_analysis/01_rankings_sector/2604_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebc00a0f969ad489/Programmazione/github/FromZeroToQuant-/14_stocks_analysis/01_rankings_sector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{214DC8CA-9975-4E2F-B63E-EB1F79706E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{214DC8CA-9975-4E2F-B63E-EB1F79706E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F45F3BCB-7903-4A9A-95BA-9B00912E84EA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{2ACEA516-618C-4DE0-B0CE-4E6013C8F2BD}"/>
   </bookViews>
@@ -1335,7 +1335,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="78.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="40.42578125" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="78.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
